--- a/input/Model_Set_and_Control.xlsx
+++ b/input/Model_Set_and_Control.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo_Projects\endemo_v2.0.0\endemo input dat\Example set\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\endemo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777809AC-B714-41B6-BB2C-0D2BE2FE047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8484084D-36D3-4A1E-A1FF-98BF4B706906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="180" windowWidth="29040" windowHeight="17520" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="730" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralSet" sheetId="22" r:id="rId1"/>
@@ -568,7 +568,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0_i"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,12 +648,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -718,7 +712,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -757,13 +751,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{394F83D0-50CC-46CD-8BEF-581C0EB643FD}"/>
     <cellStyle name="NumberCellStyle" xfId="1" xr:uid="{79ED66F4-65B5-43B8-B88C-8A58B3803A82}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="2" xr:uid="{DAD9ED8B-2FD8-446B-AD69-9D58DA8AFB98}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1092,13 +1084,13 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>1123950</xdr:colOff>
+          <xdr:colOff>1127760</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1147,14 +1139,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1176,7 +1168,7 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -1184,7 +1176,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>1143000</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1233,14 +1225,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1262,7 +1254,7 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -1270,7 +1262,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>1143000</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1319,14 +1311,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1348,7 +1340,7 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -1356,7 +1348,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>1143000</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1405,14 +1397,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1434,15 +1426,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>1133475</xdr:colOff>
+          <xdr:colOff>1135380</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1491,14 +1483,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1522,11 +1514,11 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>1123950</xdr:colOff>
+          <xdr:colOff>1127760</xdr:colOff>
           <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -1577,14 +1569,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1611,13 +1603,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>781050</xdr:colOff>
+          <xdr:colOff>784860</xdr:colOff>
           <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -1668,14 +1660,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1697,15 +1689,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1754,14 +1746,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1783,15 +1775,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1840,14 +1832,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1869,15 +1861,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1926,14 +1918,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1955,15 +1947,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2012,14 +2004,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2041,15 +2033,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2098,14 +2090,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2127,15 +2119,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2184,14 +2176,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2213,15 +2205,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2270,14 +2262,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2299,15 +2291,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2356,14 +2348,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2385,15 +2377,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2442,14 +2434,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2471,15 +2463,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2528,14 +2520,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2557,15 +2549,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2614,14 +2606,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2643,15 +2635,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2700,14 +2692,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2729,15 +2721,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>14</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2786,14 +2778,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2815,15 +2807,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>14</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2872,14 +2864,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2901,15 +2893,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>16</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2958,14 +2950,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2987,15 +2979,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>16</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3044,14 +3036,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3073,15 +3065,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3130,14 +3122,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3159,15 +3151,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3216,14 +3208,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3245,15 +3237,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>20</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3302,14 +3294,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3331,15 +3323,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>20</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3388,14 +3380,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3417,15 +3409,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3474,14 +3466,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3503,15 +3495,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>23</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3560,14 +3552,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3589,15 +3581,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>23</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3646,14 +3638,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3675,15 +3667,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>25</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3732,14 +3724,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3761,15 +3753,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>25</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3818,14 +3810,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3847,15 +3839,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>27</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3904,14 +3896,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3933,15 +3925,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>27</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>28</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3990,14 +3982,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4019,15 +4011,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>28</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>29</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4076,14 +4068,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4105,15 +4097,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>29</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>30</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4162,14 +4154,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4191,15 +4183,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>30</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>31</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4248,14 +4240,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4277,15 +4269,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>32</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>33</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4334,14 +4326,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4363,15 +4355,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4420,14 +4412,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4449,15 +4441,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
+          <xdr:colOff>754380</xdr:colOff>
           <xdr:row>33</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4506,14 +4498,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4542,13 +4534,13 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>457200</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4558,7 +4550,7 @@
                   <a14:compatExt spid="_x0000_s40963"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003A00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003A00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4597,14 +4589,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4626,15 +4618,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4644,7 +4636,7 @@
                   <a14:compatExt spid="_x0000_s40964"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004A00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004A00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4683,14 +4675,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4712,15 +4704,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4730,7 +4722,7 @@
                   <a14:compatExt spid="_x0000_s40981"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000015A00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000015A00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4769,14 +4761,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4798,15 +4790,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4816,7 +4808,7 @@
                   <a14:compatExt spid="_x0000_s40982"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000016A00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000016A00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4855,14 +4847,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4889,15 +4881,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
+          <xdr:rowOff>45720</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4907,7 +4899,7 @@
                   <a14:compatExt spid="_x0000_s11267"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000032C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000032C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4946,14 +4938,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4975,15 +4967,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4993,7 +4985,7 @@
                   <a14:compatExt spid="_x0000_s11268"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000042C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000042C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5032,14 +5024,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5061,15 +5053,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5079,7 +5071,7 @@
                   <a14:compatExt spid="_x0000_s11269"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000052C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000052C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5118,14 +5110,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5147,15 +5139,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5165,7 +5157,7 @@
                   <a14:compatExt spid="_x0000_s11270"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000062C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000062C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5204,14 +5196,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5233,13 +5225,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -5251,7 +5243,7 @@
                   <a14:compatExt spid="_x0000_s11271"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000072C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000072C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5290,14 +5282,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5319,15 +5311,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5337,7 +5329,7 @@
                   <a14:compatExt spid="_x0000_s11272"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000082C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000082C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5376,14 +5368,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5405,15 +5397,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5423,7 +5415,7 @@
                   <a14:compatExt spid="_x0000_s11273"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000092C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000092C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5462,14 +5454,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5491,15 +5483,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5509,7 +5501,7 @@
                   <a14:compatExt spid="_x0000_s11274"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000A2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5548,14 +5540,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5577,15 +5569,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5595,7 +5587,7 @@
                   <a14:compatExt spid="_x0000_s11275"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000B2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000B2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5634,14 +5626,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5663,15 +5655,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>14</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
+          <xdr:rowOff>45720</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5681,7 +5673,7 @@
                   <a14:compatExt spid="_x0000_s11276"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000C2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000C2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5720,14 +5712,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5749,15 +5741,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5767,7 +5759,7 @@
                   <a14:compatExt spid="_x0000_s11277"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000D2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000D2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5806,14 +5798,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5835,13 +5827,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>14</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>16</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
@@ -5853,7 +5845,7 @@
                   <a14:compatExt spid="_x0000_s11294"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00001E2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001E2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5892,14 +5884,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5921,15 +5913,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5939,7 +5931,7 @@
                   <a14:compatExt spid="_x0000_s11295"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00001F2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001F2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5978,14 +5970,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6007,15 +5999,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
+          <xdr:rowOff>45720</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6025,7 +6017,7 @@
                   <a14:compatExt spid="_x0000_s11303"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000272C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000272C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6064,14 +6056,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6093,15 +6085,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6111,7 +6103,7 @@
                   <a14:compatExt spid="_x0000_s11305"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000292C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000292C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6150,14 +6142,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6179,15 +6171,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
+          <xdr:rowOff>45720</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6197,7 +6189,7 @@
                   <a14:compatExt spid="_x0000_s11306"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00002A2C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002A2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6236,14 +6228,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6270,15 +6262,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>704850</xdr:rowOff>
+          <xdr:rowOff>708660</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
+          <xdr:rowOff>45720</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6288,7 +6280,7 @@
                   <a14:compatExt spid="_x0000_s15362"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-0000023C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000023C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6327,14 +6319,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6356,15 +6348,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6374,7 +6366,7 @@
                   <a14:compatExt spid="_x0000_s15363"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-0000033C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000033C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6413,14 +6405,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6442,15 +6434,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6460,7 +6452,7 @@
                   <a14:compatExt spid="_x0000_s15365"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-0000053C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000053C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6499,14 +6491,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6528,15 +6520,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6546,7 +6538,7 @@
                   <a14:compatExt spid="_x0000_s15366"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-0000063C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000063C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6585,14 +6577,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6614,15 +6606,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6632,7 +6624,7 @@
                   <a14:compatExt spid="_x0000_s15368"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-0000083C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000083C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6671,14 +6663,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6705,15 +6697,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6723,7 +6715,7 @@
                   <a14:compatExt spid="_x0000_s6148"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6762,14 +6754,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6791,15 +6783,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6809,7 +6801,7 @@
                   <a14:compatExt spid="_x0000_s6150"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000006180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6848,14 +6840,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6877,15 +6869,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6895,7 +6887,7 @@
                   <a14:compatExt spid="_x0000_s6152"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6934,14 +6926,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -6963,15 +6955,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6981,7 +6973,7 @@
                   <a14:compatExt spid="_x0000_s6154"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000A180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00000A180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7020,14 +7012,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7054,15 +7046,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7072,7 +7064,7 @@
                   <a14:compatExt spid="_x0000_s16386"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7111,14 +7103,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7140,15 +7132,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7158,7 +7150,7 @@
                   <a14:compatExt spid="_x0000_s16387"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7197,14 +7189,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7226,15 +7218,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7244,7 +7236,7 @@
                   <a14:compatExt spid="_x0000_s16388"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7283,14 +7275,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7312,15 +7304,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7330,7 +7322,7 @@
                   <a14:compatExt spid="_x0000_s16389"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000005400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7369,14 +7361,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7398,15 +7390,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7416,7 +7408,7 @@
                   <a14:compatExt spid="_x0000_s16390"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000006400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7455,14 +7447,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7484,15 +7476,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:rowOff>160020</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7502,7 +7494,7 @@
                   <a14:compatExt spid="_x0000_s16391"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000007400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7541,14 +7533,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7570,15 +7562,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>746760</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7588,7 +7580,7 @@
                   <a14:compatExt spid="_x0000_s16392"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7627,14 +7619,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-DE" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -7919,23 +7911,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB81859-A3CC-432D-8213-067363B38638}">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="90.7109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="90.6640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="4"/>
-    <col min="7" max="7" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="4"/>
-    <col min="9" max="9" width="6.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="4"/>
+    <col min="6" max="6" width="11.44140625" style="4"/>
+    <col min="7" max="7" width="10.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="4"/>
+    <col min="9" max="9" width="6.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="4"/>
     <col min="11" max="11" width="27" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="4"/>
+    <col min="12" max="16384" width="11.44140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>37</v>
       </c>
@@ -7949,7 +7941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>109</v>
       </c>
@@ -7963,7 +7955,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>110</v>
       </c>
@@ -7977,7 +7969,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>111</v>
       </c>
@@ -7991,7 +7983,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
@@ -8002,7 +7994,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>168</v>
       </c>
@@ -8013,7 +8005,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>117</v>
       </c>
@@ -8025,7 +8017,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>118</v>
       </c>
@@ -8033,7 +8025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>119</v>
       </c>
@@ -8043,7 +8035,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>47</v>
       </c>
@@ -8073,13 +8065,13 @@
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>1123950</xdr:colOff>
+                    <xdr:colOff>1127760</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8093,7 +8085,7 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>8</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
@@ -8101,7 +8093,7 @@
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>1143000</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8115,7 +8107,7 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>9</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
@@ -8123,7 +8115,7 @@
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>1143000</xdr:colOff>
                     <xdr:row>10</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8137,7 +8129,7 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>7</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
@@ -8145,7 +8137,7 @@
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>1143000</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8159,15 +8151,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>1133475</xdr:colOff>
+                    <xdr:colOff>1135380</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8183,11 +8175,11 @@
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>1123950</xdr:colOff>
+                    <xdr:colOff>1127760</xdr:colOff>
                     <xdr:row>6</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -8206,15 +8198,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B88E5B-1597-45A4-8371-3DDE149BA7E5}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="4"/>
-    <col min="3" max="3" width="22.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="4"/>
+    <col min="1" max="2" width="11.44140625" style="4"/>
+    <col min="3" max="3" width="22.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="11.44140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>166</v>
       </c>
@@ -8232,7 +8224,7 @@
       </c>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>167</v>
       </c>
@@ -8246,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>167</v>
       </c>
@@ -8260,7 +8252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>167</v>
       </c>
@@ -8274,7 +8266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>167</v>
       </c>
@@ -8288,7 +8280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>167</v>
       </c>
@@ -8302,7 +8294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>167</v>
       </c>
@@ -8316,7 +8308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>167</v>
       </c>
@@ -8330,7 +8322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>167</v>
       </c>
@@ -8344,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>167</v>
       </c>
@@ -8358,7 +8350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>167</v>
       </c>
@@ -8372,7 +8364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>167</v>
       </c>
@@ -8386,7 +8378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>167</v>
       </c>
@@ -8400,7 +8392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>167</v>
       </c>
@@ -8414,7 +8406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>167</v>
       </c>
@@ -8428,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -8442,7 +8434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>167</v>
       </c>
@@ -8456,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>167</v>
       </c>
@@ -8470,7 +8462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>167</v>
       </c>
@@ -8484,7 +8476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>167</v>
       </c>
@@ -8498,7 +8490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>167</v>
       </c>
@@ -8512,7 +8504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -8526,7 +8518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>167</v>
       </c>
@@ -8540,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>167</v>
       </c>
@@ -8554,7 +8546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>167</v>
       </c>
@@ -8568,7 +8560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>167</v>
       </c>
@@ -8582,7 +8574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>167</v>
       </c>
@@ -8596,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>167</v>
       </c>
@@ -8610,7 +8602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>167</v>
       </c>
@@ -8624,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>167</v>
       </c>
@@ -8638,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>167</v>
       </c>
@@ -8652,7 +8644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>167</v>
       </c>
@@ -8666,7 +8658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>167</v>
       </c>
@@ -8680,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>167</v>
       </c>
@@ -8694,7 +8686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>167</v>
       </c>
@@ -8723,13 +8715,13 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>781050</xdr:colOff>
+                    <xdr:colOff>784860</xdr:colOff>
                     <xdr:row>2</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -8745,15 +8737,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8767,15 +8759,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8789,15 +8781,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8811,15 +8803,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8833,15 +8825,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8855,15 +8847,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8877,15 +8869,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8899,15 +8891,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8921,15 +8913,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>10</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8943,15 +8935,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>10</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>11</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8965,15 +8957,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>11</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>12</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8987,15 +8979,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>12</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>13</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9009,15 +9001,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>13</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>14</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9031,15 +9023,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>14</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>15</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9053,15 +9045,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>15</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>16</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9075,15 +9067,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>16</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>17</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9097,15 +9089,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>17</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>18</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9119,15 +9111,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>18</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>19</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9141,15 +9133,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>19</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>20</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9163,15 +9155,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>20</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9185,15 +9177,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>22</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9207,15 +9199,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>22</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>23</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9229,15 +9221,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>23</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>24</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9251,15 +9243,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>24</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>25</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9273,15 +9265,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>25</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>26</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9295,15 +9287,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>26</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>27</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9317,15 +9309,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>27</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>28</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9339,15 +9331,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>28</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>29</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9361,15 +9353,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>29</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>30</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9383,15 +9375,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>30</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>31</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9405,15 +9397,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>32</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>33</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9427,15 +9419,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>34</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9449,15 +9441,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>32</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
+                    <xdr:colOff>754380</xdr:colOff>
                     <xdr:row>33</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9474,15 +9466,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E8C7D2-1A7F-4BFA-A614-FE10658E33CA}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="54" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>67</v>
       </c>
@@ -9500,7 +9492,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>68</v>
       </c>
@@ -9512,7 +9504,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>69</v>
       </c>
@@ -9524,7 +9516,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>71</v>
       </c>
@@ -9536,7 +9528,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>70</v>
       </c>
@@ -9548,7 +9540,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -9567,13 +9559,13 @@
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>457200</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9587,15 +9579,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>1</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>476250</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9609,15 +9601,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>2</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>476250</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9631,15 +9623,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>476250</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9656,22 +9648,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E5C615-F815-41AB-BEEF-C7C927BFC703}">
   <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="45.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -9697,7 +9689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -9724,7 +9716,7 @@
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -9739,7 +9731,7 @@
       <c r="H3" s="8"/>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -9753,7 +9745,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -9767,7 +9759,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -9782,7 +9774,7 @@
       <c r="H6" s="8"/>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -9796,7 +9788,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>56</v>
       </c>
@@ -9811,7 +9803,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -9827,7 +9819,7 @@
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>58</v>
       </c>
@@ -9843,7 +9835,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>59</v>
       </c>
@@ -9859,7 +9851,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
@@ -9875,7 +9867,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -9891,7 +9883,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -9905,7 +9897,7 @@
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -9920,7 +9912,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -9935,7 +9927,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -9951,7 +9943,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
@@ -9974,15 +9966,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>14</xdr:row>
-                    <xdr:rowOff>47625</xdr:rowOff>
+                    <xdr:rowOff>45720</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9996,15 +9988,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>13</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>15</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10018,13 +10010,13 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>14</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>16</xdr:row>
                     <xdr:rowOff>38100</xdr:rowOff>
                   </to>
@@ -10040,15 +10032,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>47625</xdr:rowOff>
+                    <xdr:rowOff>45720</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10062,15 +10054,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10084,15 +10076,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10106,15 +10098,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10128,13 +10120,13 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>8</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -10150,15 +10142,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>9</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10172,15 +10164,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>11</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10194,15 +10186,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>10</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>12</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10216,15 +10208,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>11</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>13</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10238,15 +10230,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10260,15 +10252,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>47625</xdr:rowOff>
+                    <xdr:rowOff>45720</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10282,15 +10274,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10304,15 +10296,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>16</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>17</xdr:row>
-                    <xdr:rowOff>47625</xdr:rowOff>
+                    <xdr:rowOff>45720</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10329,18 +10321,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1B068A-2F09-4A83-8CB8-90B482ECFD1D}">
   <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -10363,7 +10355,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -10372,9 +10364,9 @@
         <v>0</v>
       </c>
       <c r="E2" s="9"/>
-      <c r="G2" s="26"/>
+      <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>77</v>
       </c>
@@ -10383,9 +10375,9 @@
         <v>0</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="G3" s="26"/>
+      <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -10394,9 +10386,8 @@
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="27"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>115</v>
       </c>
@@ -10405,7 +10396,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>78</v>
       </c>
@@ -10432,15 +10423,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>704850</xdr:rowOff>
+                    <xdr:rowOff>708660</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>47625</xdr:rowOff>
+                    <xdr:rowOff>45720</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10454,15 +10445,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10476,15 +10467,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10498,15 +10489,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10520,15 +10511,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10545,21 +10536,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -10591,7 +10582,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>105</v>
       </c>
@@ -10603,7 +10594,7 @@
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>106</v>
       </c>
@@ -10614,7 +10605,7 @@
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>107</v>
       </c>
@@ -10626,7 +10617,7 @@
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>108</v>
       </c>
@@ -10638,10 +10629,10 @@
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I6" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H8" s="15"/>
     </row>
   </sheetData>
@@ -10662,15 +10653,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10684,15 +10675,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10706,15 +10697,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10728,15 +10719,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10753,16 +10744,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B06B0BC-80A2-4612-8E23-3219E6469DB3}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -10779,7 +10770,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -10789,7 +10780,7 @@
       </c>
       <c r="E2" s="8"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -10799,7 +10790,7 @@
       </c>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -10808,7 +10799,7 @@
       </c>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -10817,7 +10808,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -10826,7 +10817,7 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -10835,7 +10826,7 @@
       </c>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -10862,15 +10853,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10884,15 +10875,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10906,15 +10897,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10928,15 +10919,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10950,15 +10941,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10972,15 +10963,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:rowOff>160020</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10994,15 +10985,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>1</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>746760</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -11019,13 +11010,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29C1E7A-19BF-4F80-B658-BBD8EDEBB672}">
   <sheetPr codeName="Tabelle8"/>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>123</v>
       </c>
@@ -11039,7 +11030,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -11053,7 +11044,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -11067,7 +11058,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -11081,7 +11072,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
         <v>101</v>
       </c>
@@ -11092,7 +11083,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="13" t="s">
         <v>129</v>
       </c>
@@ -11101,26 +11092,26 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8" s="13"/>
       <c r="D8" s="13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9" s="13"/>
       <c r="D9" s="13" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="13"/>
       <c r="D10" s="13" t="s">
         <v>93</v>
